--- a/TeplosilaWeb/Content/properties/htrv.xlsx
+++ b/TeplosilaWeb/Content/properties/htrv.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pge27\OneDrive\Рабочий стол\TeploSilaWeb\TeplosilaWeb\Content\properties\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{37BBCE5E-9C05-4C02-BC2C-9C5D091A4E05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1505C588-DE37-4702-909D-88FAD73368D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-5025" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -146,15 +146,6 @@
     <t>Наличие функции безопасности (возврат)</t>
   </si>
   <si>
-    <t>TSL-1600-25-2-24-IP67</t>
-  </si>
-  <si>
-    <t>TSL-2200-40-2-24-IP67</t>
-  </si>
-  <si>
-    <t>TSL-3000-60-2-24-IP67</t>
-  </si>
-  <si>
     <t>TSL-1600-25-2T-230-IP67</t>
   </si>
   <si>
@@ -162,6 +153,15 @@
   </si>
   <si>
     <t>TSL-3000-60-2T-230-IP67</t>
+  </si>
+  <si>
+    <t>TSL-1600-25-2М-24-IP67</t>
+  </si>
+  <si>
+    <t>TSL-2200-40-2М-24-IP67</t>
+  </si>
+  <si>
+    <t>TSL-3000-60-2М-24-IP67</t>
   </si>
 </sst>
 </file>
@@ -366,6 +366,12 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -378,14 +384,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -682,50 +682,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="19"/>
-      <c r="P1" s="19"/>
-      <c r="Q1" s="19"/>
-      <c r="R1" s="19"/>
-      <c r="S1" s="19"/>
-      <c r="T1" s="19"/>
-      <c r="U1" s="19"/>
-      <c r="V1" s="19"/>
-      <c r="W1" s="19"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="13"/>
+      <c r="S1" s="13"/>
+      <c r="T1" s="13"/>
+      <c r="U1" s="13"/>
+      <c r="V1" s="13"/>
+      <c r="W1" s="13"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B2" s="3">
         <v>53</v>
       </c>
-      <c r="C2" s="16">
+      <c r="C2" s="18">
         <v>54</v>
       </c>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
+      <c r="L2" s="18"/>
+      <c r="M2" s="18"/>
+      <c r="N2" s="18"/>
       <c r="O2" s="3">
         <v>55</v>
       </c>
@@ -755,88 +755,88 @@
       </c>
     </row>
     <row r="3" spans="1:23" s="2" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="14"/>
-      <c r="M3" s="14"/>
-      <c r="N3" s="15"/>
-      <c r="O3" s="17" t="s">
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="16"/>
+      <c r="L3" s="16"/>
+      <c r="M3" s="16"/>
+      <c r="N3" s="17"/>
+      <c r="O3" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="P3" s="17"/>
-      <c r="Q3" s="17" t="s">
+      <c r="P3" s="14"/>
+      <c r="Q3" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="R3" s="17" t="s">
+      <c r="R3" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="S3" s="17" t="s">
+      <c r="S3" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="T3" s="17"/>
-      <c r="U3" s="17" t="s">
+      <c r="T3" s="14"/>
+      <c r="U3" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="V3" s="17" t="s">
+      <c r="V3" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="W3" s="17" t="s">
+      <c r="W3" s="14" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:23" s="2" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="18"/>
-      <c r="B4" s="18"/>
-      <c r="C4" s="13" t="s">
+      <c r="A4" s="19"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="14"/>
-      <c r="K4" s="14"/>
-      <c r="L4" s="14"/>
-      <c r="M4" s="14"/>
-      <c r="N4" s="15"/>
-      <c r="O4" s="17" t="s">
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="16"/>
+      <c r="K4" s="16"/>
+      <c r="L4" s="16"/>
+      <c r="M4" s="16"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="P4" s="17" t="s">
+      <c r="P4" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="Q4" s="17"/>
-      <c r="R4" s="17"/>
-      <c r="S4" s="17" t="s">
+      <c r="Q4" s="14"/>
+      <c r="R4" s="14"/>
+      <c r="S4" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="T4" s="17" t="s">
+      <c r="T4" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="U4" s="17"/>
-      <c r="V4" s="17"/>
-      <c r="W4" s="17"/>
+      <c r="U4" s="14"/>
+      <c r="V4" s="14"/>
+      <c r="W4" s="14"/>
     </row>
     <row r="5" spans="1:23" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="18"/>
-      <c r="B5" s="18"/>
+      <c r="A5" s="19"/>
+      <c r="B5" s="19"/>
       <c r="C5" s="4">
         <v>15</v>
       </c>
@@ -873,15 +873,15 @@
       <c r="N5" s="4">
         <v>200</v>
       </c>
-      <c r="O5" s="17"/>
-      <c r="P5" s="17"/>
-      <c r="Q5" s="17"/>
-      <c r="R5" s="17"/>
-      <c r="S5" s="17"/>
-      <c r="T5" s="17"/>
-      <c r="U5" s="17"/>
-      <c r="V5" s="17"/>
-      <c r="W5" s="17"/>
+      <c r="O5" s="14"/>
+      <c r="P5" s="14"/>
+      <c r="Q5" s="14"/>
+      <c r="R5" s="14"/>
+      <c r="S5" s="14"/>
+      <c r="T5" s="14"/>
+      <c r="U5" s="14"/>
+      <c r="V5" s="14"/>
+      <c r="W5" s="14"/>
     </row>
     <row r="6" spans="1:23" s="1" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A6" s="5">
@@ -1006,7 +1006,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C8" s="7">
         <v>16</v>
@@ -1065,7 +1065,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C9" s="9">
         <v>16</v>
@@ -1525,7 +1525,7 @@
         <v>12</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
@@ -1578,7 +1578,7 @@
         <v>13</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
@@ -1949,7 +1949,7 @@
         <v>20</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
@@ -2002,7 +2002,7 @@
         <v>21</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="12"/>
@@ -2159,6 +2159,7 @@
     <row r="29" spans="1:23" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B3:B5"/>
     <mergeCell ref="A1:W1"/>
     <mergeCell ref="W3:W5"/>
     <mergeCell ref="S3:T3"/>
@@ -2175,7 +2176,6 @@
     <mergeCell ref="C2:N2"/>
     <mergeCell ref="R3:R5"/>
     <mergeCell ref="A3:A5"/>
-    <mergeCell ref="B3:B5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/TeplosilaWeb/Content/properties/htrv.xlsx
+++ b/TeplosilaWeb/Content/properties/htrv.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pge27\OneDrive\Рабочий стол\TeploSilaWeb\TeplosilaWeb\Content\properties\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user29\Documents\ТЗ программа подбора TRV, RDT\ТЗ клапаны TRV\25.05.2026 (действ)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1505C588-DE37-4702-909D-88FAD73368D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4656783-031E-4411-A8E2-192AABC9EACD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -20,9 +20,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -33,13 +30,7 @@
     <t>Условный диаметр DN, мм</t>
   </si>
   <si>
-    <t>TSL-1600-25-1-230-IP67</t>
-  </si>
-  <si>
     <t>TSL-1600-25-1R-230-IP67</t>
-  </si>
-  <si>
-    <t>TSL-2200-40-1-230-IP67</t>
   </si>
   <si>
     <t>TSL-2200-40-1R-230-IP67</t>
@@ -89,9 +80,6 @@
   </si>
   <si>
     <t>24 VAC/DC</t>
-  </si>
-  <si>
-    <t>TSL-3000-60-1-230-IP67</t>
   </si>
   <si>
     <t>TRV, TRV-T</t>
@@ -162,25 +150,25 @@
   </si>
   <si>
     <t>TSL-3000-60-2М-24-IP67</t>
+  </si>
+  <si>
+    <t>TSL-1600-25-2М-230-IP67</t>
+  </si>
+  <si>
+    <t>TSL-2200-40-2М-230-IP67</t>
+  </si>
+  <si>
+    <t>TSL-3000-60-2М-230-IP67</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF212121"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
@@ -213,13 +201,13 @@
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
     </font>
     <font>
       <sz val="10"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
@@ -227,7 +215,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
@@ -235,18 +222,10 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
     </font>
   </fonts>
   <fills count="2">
@@ -330,46 +309,38 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -381,11 +352,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -670,273 +638,274 @@
   <dimension ref="A1:W29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.7109375" customWidth="1"/>
-    <col min="2" max="2" width="22.28515625" customWidth="1"/>
-    <col min="3" max="14" width="4.5703125" customWidth="1"/>
-    <col min="18" max="18" width="13.85546875" customWidth="1"/>
-    <col min="19" max="19" width="10.140625" customWidth="1"/>
-    <col min="20" max="20" width="11.140625" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" customWidth="1"/>
-    <col min="22" max="22" width="12" customWidth="1"/>
-    <col min="23" max="23" width="13.28515625" customWidth="1"/>
+    <col min="1" max="1" width="6.7109375" style="7" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" style="7" customWidth="1"/>
+    <col min="3" max="14" width="4.5703125" style="7" customWidth="1"/>
+    <col min="15" max="17" width="9.140625" style="7"/>
+    <col min="18" max="18" width="13.85546875" style="7" customWidth="1"/>
+    <col min="19" max="19" width="10.140625" style="7" customWidth="1"/>
+    <col min="20" max="20" width="11.140625" style="7" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="7" customWidth="1"/>
+    <col min="22" max="22" width="12" style="7" customWidth="1"/>
+    <col min="23" max="23" width="13.28515625" style="7" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
-      <c r="Q1" s="13"/>
-      <c r="R1" s="13"/>
-      <c r="S1" s="13"/>
-      <c r="T1" s="13"/>
-      <c r="U1" s="13"/>
-      <c r="V1" s="13"/>
-      <c r="W1" s="13"/>
+      <c r="A1" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
+      <c r="M1" s="11"/>
+      <c r="N1" s="11"/>
+      <c r="O1" s="11"/>
+      <c r="P1" s="11"/>
+      <c r="Q1" s="11"/>
+      <c r="R1" s="11"/>
+      <c r="S1" s="11"/>
+      <c r="T1" s="11"/>
+      <c r="U1" s="11"/>
+      <c r="V1" s="11"/>
+      <c r="W1" s="11"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="B2" s="3">
+      <c r="B2" s="8">
         <v>53</v>
       </c>
-      <c r="C2" s="18">
+      <c r="C2" s="16">
         <v>54</v>
       </c>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="18"/>
-      <c r="L2" s="18"/>
-      <c r="M2" s="18"/>
-      <c r="N2" s="18"/>
-      <c r="O2" s="3">
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="16"/>
+      <c r="O2" s="8">
         <v>55</v>
       </c>
-      <c r="P2" s="3">
+      <c r="P2" s="8">
         <v>56</v>
       </c>
-      <c r="Q2" s="3">
+      <c r="Q2" s="8">
         <v>57</v>
       </c>
-      <c r="R2" s="3">
+      <c r="R2" s="8">
         <v>58</v>
       </c>
-      <c r="S2" s="3">
+      <c r="S2" s="8">
         <v>59</v>
       </c>
-      <c r="T2" s="3">
+      <c r="T2" s="8">
         <v>60</v>
       </c>
-      <c r="U2" s="3">
+      <c r="U2" s="8">
         <v>61</v>
       </c>
-      <c r="V2" s="3">
+      <c r="V2" s="8">
         <v>62</v>
       </c>
-      <c r="W2" s="3">
+      <c r="W2" s="8">
         <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:23" s="2" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="C3" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="14"/>
+      <c r="M3" s="14"/>
+      <c r="N3" s="15"/>
+      <c r="O3" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="P3" s="12"/>
+      <c r="Q3" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="R3" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="S3" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="T3" s="12"/>
+      <c r="U3" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="V3" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="W3" s="12" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" s="2" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="12"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
+      <c r="N4" s="15"/>
+      <c r="O4" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
-      <c r="I3" s="16"/>
-      <c r="J3" s="16"/>
-      <c r="K3" s="16"/>
-      <c r="L3" s="16"/>
-      <c r="M3" s="16"/>
-      <c r="N3" s="17"/>
-      <c r="O3" s="14" t="s">
+      <c r="P4" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="P3" s="14"/>
-      <c r="Q3" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="R3" s="14" t="s">
+      <c r="Q4" s="12"/>
+      <c r="R4" s="12"/>
+      <c r="S4" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="S3" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="T3" s="14"/>
-      <c r="U3" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="V3" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="W3" s="14" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23" s="2" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="19"/>
-      <c r="B4" s="19"/>
-      <c r="C4" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="16"/>
-      <c r="K4" s="16"/>
-      <c r="L4" s="16"/>
-      <c r="M4" s="16"/>
-      <c r="N4" s="17"/>
-      <c r="O4" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="P4" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q4" s="14"/>
-      <c r="R4" s="14"/>
-      <c r="S4" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="T4" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="U4" s="14"/>
-      <c r="V4" s="14"/>
-      <c r="W4" s="14"/>
+      <c r="T4" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="U4" s="12"/>
+      <c r="V4" s="12"/>
+      <c r="W4" s="12"/>
     </row>
     <row r="5" spans="1:23" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="19"/>
-      <c r="B5" s="19"/>
-      <c r="C5" s="4">
-        <v>15</v>
-      </c>
-      <c r="D5" s="4">
+      <c r="A5" s="12"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="3">
+        <v>15</v>
+      </c>
+      <c r="D5" s="3">
         <v>20</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="3">
         <v>25</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="3">
         <v>32</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5" s="3">
         <v>40</v>
       </c>
-      <c r="H5" s="4">
+      <c r="H5" s="3">
         <v>50</v>
       </c>
-      <c r="I5" s="4">
+      <c r="I5" s="3">
         <v>65</v>
       </c>
-      <c r="J5" s="4">
+      <c r="J5" s="3">
         <v>80</v>
       </c>
-      <c r="K5" s="4">
+      <c r="K5" s="3">
         <v>100</v>
       </c>
-      <c r="L5" s="4">
+      <c r="L5" s="3">
         <v>125</v>
       </c>
-      <c r="M5" s="4">
+      <c r="M5" s="3">
         <v>150</v>
       </c>
-      <c r="N5" s="4">
+      <c r="N5" s="3">
         <v>200</v>
       </c>
-      <c r="O5" s="14"/>
-      <c r="P5" s="14"/>
-      <c r="Q5" s="14"/>
-      <c r="R5" s="14"/>
-      <c r="S5" s="14"/>
-      <c r="T5" s="14"/>
-      <c r="U5" s="14"/>
-      <c r="V5" s="14"/>
-      <c r="W5" s="14"/>
+      <c r="O5" s="12"/>
+      <c r="P5" s="12"/>
+      <c r="Q5" s="12"/>
+      <c r="R5" s="12"/>
+      <c r="S5" s="12"/>
+      <c r="T5" s="12"/>
+      <c r="U5" s="12"/>
+      <c r="V5" s="12"/>
+      <c r="W5" s="12"/>
     </row>
     <row r="6" spans="1:23" s="1" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A6" s="5">
         <v>1</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="7">
-        <v>16</v>
-      </c>
-      <c r="D6" s="7">
-        <v>16</v>
-      </c>
-      <c r="E6" s="7">
-        <v>16</v>
-      </c>
-      <c r="F6" s="7">
-        <v>16</v>
-      </c>
-      <c r="G6" s="7">
-        <v>16</v>
-      </c>
-      <c r="H6" s="7">
-        <v>16</v>
-      </c>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
+        <v>40</v>
+      </c>
+      <c r="C6" s="5">
+        <v>16</v>
+      </c>
+      <c r="D6" s="5">
+        <v>16</v>
+      </c>
+      <c r="E6" s="5">
+        <v>16</v>
+      </c>
+      <c r="F6" s="5">
+        <v>16</v>
+      </c>
+      <c r="G6" s="5">
+        <v>16</v>
+      </c>
+      <c r="H6" s="5">
+        <v>16</v>
+      </c>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
       <c r="O6" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Q6" s="5">
         <v>1600</v>
       </c>
-      <c r="R6" s="8" t="s">
-        <v>18</v>
+      <c r="R6" s="9" t="s">
+        <v>16</v>
       </c>
       <c r="S6" s="5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T6" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="U6" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="V6" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="W6" s="5">
         <v>10</v>
@@ -946,56 +915,56 @@
       <c r="A7" s="5">
         <v>2</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C7" s="7">
-        <v>16</v>
-      </c>
-      <c r="D7" s="7">
-        <v>16</v>
-      </c>
-      <c r="E7" s="7">
-        <v>16</v>
-      </c>
-      <c r="F7" s="7">
-        <v>16</v>
-      </c>
-      <c r="G7" s="7">
-        <v>16</v>
-      </c>
-      <c r="H7" s="7">
-        <v>16</v>
-      </c>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="7"/>
+      <c r="B7" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="5">
+        <v>16</v>
+      </c>
+      <c r="D7" s="5">
+        <v>16</v>
+      </c>
+      <c r="E7" s="5">
+        <v>16</v>
+      </c>
+      <c r="F7" s="5">
+        <v>16</v>
+      </c>
+      <c r="G7" s="5">
+        <v>16</v>
+      </c>
+      <c r="H7" s="5">
+        <v>16</v>
+      </c>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="5"/>
       <c r="O7" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="P7" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Q7" s="5">
         <v>1600</v>
       </c>
-      <c r="R7" s="8" t="s">
-        <v>18</v>
+      <c r="R7" s="9" t="s">
+        <v>16</v>
       </c>
       <c r="S7" s="5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T7" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="U7" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="V7" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="W7" s="5">
         <v>10</v>
@@ -1005,117 +974,117 @@
       <c r="A8" s="5">
         <v>3</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" s="7">
-        <v>16</v>
-      </c>
-      <c r="D8" s="7">
-        <v>16</v>
-      </c>
-      <c r="E8" s="7">
-        <v>16</v>
-      </c>
-      <c r="F8" s="7">
-        <v>16</v>
-      </c>
-      <c r="G8" s="7">
-        <v>16</v>
-      </c>
-      <c r="H8" s="7">
-        <v>16</v>
-      </c>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-      <c r="N8" s="7"/>
+      <c r="B8" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="5">
+        <v>16</v>
+      </c>
+      <c r="D8" s="5">
+        <v>16</v>
+      </c>
+      <c r="E8" s="5">
+        <v>16</v>
+      </c>
+      <c r="F8" s="5">
+        <v>16</v>
+      </c>
+      <c r="G8" s="5">
+        <v>16</v>
+      </c>
+      <c r="H8" s="5">
+        <v>16</v>
+      </c>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
       <c r="O8" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="P8" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Q8" s="5">
         <v>1600</v>
       </c>
-      <c r="R8" s="8" t="s">
-        <v>18</v>
+      <c r="R8" s="9" t="s">
+        <v>16</v>
       </c>
       <c r="S8" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="T8" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="U8" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="V8" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="W8" s="5">
         <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:23" s="1" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A9" s="9">
+      <c r="A9" s="5">
         <v>4</v>
       </c>
-      <c r="B9" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" s="9">
-        <v>16</v>
-      </c>
-      <c r="D9" s="9">
-        <v>16</v>
-      </c>
-      <c r="E9" s="9">
-        <v>16</v>
-      </c>
-      <c r="F9" s="9">
-        <v>16</v>
-      </c>
-      <c r="G9" s="9">
-        <v>16</v>
-      </c>
-      <c r="H9" s="9">
-        <v>16</v>
-      </c>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
-      <c r="N9" s="9"/>
-      <c r="O9" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="P9" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q9" s="9">
+      <c r="B9" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="5">
+        <v>16</v>
+      </c>
+      <c r="D9" s="5">
+        <v>16</v>
+      </c>
+      <c r="E9" s="5">
+        <v>16</v>
+      </c>
+      <c r="F9" s="5">
+        <v>16</v>
+      </c>
+      <c r="G9" s="5">
+        <v>16</v>
+      </c>
+      <c r="H9" s="5">
+        <v>16</v>
+      </c>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="P9" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q9" s="5">
         <v>1600</v>
       </c>
-      <c r="R9" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="S9" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="T9" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="U9" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="V9" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="W9" s="9">
+      <c r="R9" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="S9" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="T9" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="U9" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="V9" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="W9" s="5">
         <v>10</v>
       </c>
     </row>
@@ -1123,56 +1092,56 @@
       <c r="A10" s="5">
         <v>5</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="7">
-        <v>16</v>
-      </c>
-      <c r="D10" s="7">
-        <v>16</v>
-      </c>
-      <c r="E10" s="7">
-        <v>16</v>
-      </c>
-      <c r="F10" s="7">
-        <v>16</v>
-      </c>
-      <c r="G10" s="7">
-        <v>16</v>
-      </c>
-      <c r="H10" s="7">
-        <v>16</v>
-      </c>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
-      <c r="N10" s="7"/>
+      <c r="B10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="5">
+        <v>16</v>
+      </c>
+      <c r="D10" s="5">
+        <v>16</v>
+      </c>
+      <c r="E10" s="5">
+        <v>16</v>
+      </c>
+      <c r="F10" s="5">
+        <v>16</v>
+      </c>
+      <c r="G10" s="5">
+        <v>16</v>
+      </c>
+      <c r="H10" s="5">
+        <v>16</v>
+      </c>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="5"/>
+      <c r="N10" s="5"/>
       <c r="O10" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="P10" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Q10" s="5">
         <v>1600</v>
       </c>
-      <c r="R10" s="8" t="s">
-        <v>18</v>
+      <c r="R10" s="9" t="s">
+        <v>16</v>
       </c>
       <c r="S10" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="T10" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="U10" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="V10" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="W10" s="5">
         <v>10</v>
@@ -1182,56 +1151,56 @@
       <c r="A11" s="5">
         <v>6</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="7">
-        <v>16</v>
-      </c>
-      <c r="D11" s="7">
-        <v>16</v>
-      </c>
-      <c r="E11" s="7">
-        <v>16</v>
-      </c>
-      <c r="F11" s="7">
-        <v>16</v>
-      </c>
-      <c r="G11" s="7">
-        <v>16</v>
-      </c>
-      <c r="H11" s="7">
-        <v>16</v>
-      </c>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
-      <c r="M11" s="7"/>
-      <c r="N11" s="7"/>
+      <c r="B11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="5">
+        <v>16</v>
+      </c>
+      <c r="D11" s="5">
+        <v>16</v>
+      </c>
+      <c r="E11" s="5">
+        <v>16</v>
+      </c>
+      <c r="F11" s="5">
+        <v>16</v>
+      </c>
+      <c r="G11" s="5">
+        <v>16</v>
+      </c>
+      <c r="H11" s="5">
+        <v>16</v>
+      </c>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="5"/>
+      <c r="M11" s="5"/>
+      <c r="N11" s="5"/>
       <c r="O11" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="P11" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Q11" s="5">
         <v>1600</v>
       </c>
-      <c r="R11" s="8" t="s">
-        <v>18</v>
+      <c r="R11" s="9" t="s">
+        <v>16</v>
       </c>
       <c r="S11" s="5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T11" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="U11" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="V11" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="W11" s="5">
         <v>8</v>
@@ -1241,56 +1210,56 @@
       <c r="A12" s="5">
         <v>7</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="7">
-        <v>16</v>
-      </c>
-      <c r="D12" s="7">
-        <v>16</v>
-      </c>
-      <c r="E12" s="7">
-        <v>16</v>
-      </c>
-      <c r="F12" s="7">
-        <v>16</v>
-      </c>
-      <c r="G12" s="7">
-        <v>16</v>
-      </c>
-      <c r="H12" s="7">
-        <v>16</v>
-      </c>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
-      <c r="M12" s="7"/>
-      <c r="N12" s="7"/>
+      <c r="B12" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="5">
+        <v>16</v>
+      </c>
+      <c r="D12" s="5">
+        <v>16</v>
+      </c>
+      <c r="E12" s="5">
+        <v>16</v>
+      </c>
+      <c r="F12" s="5">
+        <v>16</v>
+      </c>
+      <c r="G12" s="5">
+        <v>16</v>
+      </c>
+      <c r="H12" s="5">
+        <v>16</v>
+      </c>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="5"/>
+      <c r="M12" s="5"/>
+      <c r="N12" s="5"/>
       <c r="O12" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="P12" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Q12" s="5">
         <v>1600</v>
       </c>
-      <c r="R12" s="8" t="s">
-        <v>18</v>
+      <c r="R12" s="9" t="s">
+        <v>16</v>
       </c>
       <c r="S12" s="5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T12" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="U12" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="V12" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="W12" s="5">
         <v>8</v>
@@ -1300,56 +1269,56 @@
       <c r="A13" s="5">
         <v>8</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="7">
-        <v>16</v>
-      </c>
-      <c r="D13" s="7">
-        <v>16</v>
-      </c>
-      <c r="E13" s="7">
-        <v>16</v>
-      </c>
-      <c r="F13" s="7">
-        <v>16</v>
-      </c>
-      <c r="G13" s="7">
-        <v>16</v>
-      </c>
-      <c r="H13" s="7">
-        <v>16</v>
-      </c>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="7"/>
+      <c r="B13" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="5">
+        <v>16</v>
+      </c>
+      <c r="D13" s="5">
+        <v>16</v>
+      </c>
+      <c r="E13" s="5">
+        <v>16</v>
+      </c>
+      <c r="F13" s="5">
+        <v>16</v>
+      </c>
+      <c r="G13" s="5">
+        <v>16</v>
+      </c>
+      <c r="H13" s="5">
+        <v>16</v>
+      </c>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="5"/>
+      <c r="N13" s="5"/>
       <c r="O13" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="P13" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Q13" s="5">
         <v>1600</v>
       </c>
-      <c r="R13" s="8" t="s">
-        <v>18</v>
+      <c r="R13" s="9" t="s">
+        <v>16</v>
       </c>
       <c r="S13" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="T13" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="U13" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="V13" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="W13" s="5">
         <v>8</v>
@@ -1359,56 +1328,56 @@
       <c r="A14" s="5">
         <v>9</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="7">
-        <v>16</v>
-      </c>
-      <c r="D14" s="7">
-        <v>16</v>
-      </c>
-      <c r="E14" s="7">
-        <v>16</v>
-      </c>
-      <c r="F14" s="7">
-        <v>16</v>
-      </c>
-      <c r="G14" s="7">
-        <v>16</v>
-      </c>
-      <c r="H14" s="7">
-        <v>16</v>
-      </c>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7"/>
-      <c r="N14" s="7"/>
+      <c r="B14" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="5">
+        <v>16</v>
+      </c>
+      <c r="D14" s="5">
+        <v>16</v>
+      </c>
+      <c r="E14" s="5">
+        <v>16</v>
+      </c>
+      <c r="F14" s="5">
+        <v>16</v>
+      </c>
+      <c r="G14" s="5">
+        <v>16</v>
+      </c>
+      <c r="H14" s="5">
+        <v>16</v>
+      </c>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="5"/>
+      <c r="N14" s="5"/>
       <c r="O14" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="P14" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Q14" s="5">
         <v>1600</v>
       </c>
-      <c r="R14" s="8" t="s">
-        <v>18</v>
+      <c r="R14" s="9" t="s">
+        <v>16</v>
       </c>
       <c r="S14" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="T14" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="U14" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="V14" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="W14" s="5">
         <v>8</v>
@@ -1419,49 +1388,49 @@
         <v>10</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7">
-        <v>16</v>
-      </c>
-      <c r="J15" s="7">
-        <v>16</v>
-      </c>
-      <c r="K15" s="7">
-        <v>16</v>
-      </c>
-      <c r="L15" s="7"/>
-      <c r="M15" s="7"/>
-      <c r="N15" s="7"/>
+        <v>41</v>
+      </c>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5">
+        <v>16</v>
+      </c>
+      <c r="J15" s="5">
+        <v>16</v>
+      </c>
+      <c r="K15" s="5">
+        <v>16</v>
+      </c>
+      <c r="L15" s="5"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="5"/>
       <c r="O15" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="P15" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Q15" s="5">
         <v>2200</v>
       </c>
-      <c r="R15" s="8" t="s">
-        <v>18</v>
+      <c r="R15" s="9" t="s">
+        <v>16</v>
       </c>
       <c r="S15" s="5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T15" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="U15" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="V15" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="W15" s="5">
         <v>10</v>
@@ -1471,50 +1440,50 @@
       <c r="A16" s="5">
         <v>11</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7">
-        <v>16</v>
-      </c>
-      <c r="J16" s="7">
-        <v>16</v>
-      </c>
-      <c r="K16" s="7">
-        <v>16</v>
-      </c>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7"/>
-      <c r="N16" s="7"/>
+      <c r="B16" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5">
+        <v>16</v>
+      </c>
+      <c r="J16" s="5">
+        <v>16</v>
+      </c>
+      <c r="K16" s="5">
+        <v>16</v>
+      </c>
+      <c r="L16" s="5"/>
+      <c r="M16" s="5"/>
+      <c r="N16" s="5"/>
       <c r="O16" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="P16" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Q16" s="5">
         <v>2200</v>
       </c>
-      <c r="R16" s="8" t="s">
-        <v>18</v>
+      <c r="R16" s="9" t="s">
+        <v>16</v>
       </c>
       <c r="S16" s="5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T16" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="U16" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="V16" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="W16" s="5">
         <v>10</v>
@@ -1524,105 +1493,105 @@
       <c r="A17" s="5">
         <v>12</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7">
-        <v>16</v>
-      </c>
-      <c r="J17" s="7">
-        <v>16</v>
-      </c>
-      <c r="K17" s="7">
-        <v>16</v>
-      </c>
-      <c r="L17" s="7"/>
-      <c r="M17" s="7"/>
-      <c r="N17" s="7"/>
+      <c r="B17" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5">
+        <v>16</v>
+      </c>
+      <c r="J17" s="5">
+        <v>16</v>
+      </c>
+      <c r="K17" s="5">
+        <v>16</v>
+      </c>
+      <c r="L17" s="5"/>
+      <c r="M17" s="5"/>
+      <c r="N17" s="5"/>
       <c r="O17" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="P17" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Q17" s="5">
         <v>2200</v>
       </c>
-      <c r="R17" s="8" t="s">
-        <v>18</v>
+      <c r="R17" s="9" t="s">
+        <v>16</v>
       </c>
       <c r="S17" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="T17" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="U17" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="V17" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="W17" s="5">
         <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:23" s="1" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A18" s="9">
+      <c r="A18" s="5">
         <v>13</v>
       </c>
-      <c r="B18" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9">
-        <v>16</v>
-      </c>
-      <c r="J18" s="9">
-        <v>16</v>
-      </c>
-      <c r="K18" s="9">
-        <v>16</v>
-      </c>
-      <c r="L18" s="9"/>
-      <c r="M18" s="9"/>
-      <c r="N18" s="9"/>
-      <c r="O18" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="P18" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q18" s="9">
+      <c r="B18" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5">
+        <v>16</v>
+      </c>
+      <c r="J18" s="5">
+        <v>16</v>
+      </c>
+      <c r="K18" s="5">
+        <v>16</v>
+      </c>
+      <c r="L18" s="5"/>
+      <c r="M18" s="5"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="P18" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q18" s="5">
         <v>2200</v>
       </c>
-      <c r="R18" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="S18" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="T18" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="U18" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="V18" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="W18" s="9">
+      <c r="R18" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="S18" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="T18" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="U18" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="V18" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="W18" s="5">
         <v>10</v>
       </c>
     </row>
@@ -1630,50 +1599,50 @@
       <c r="A19" s="5">
         <v>14</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7">
-        <v>16</v>
-      </c>
-      <c r="J19" s="7">
-        <v>16</v>
-      </c>
-      <c r="K19" s="7">
-        <v>16</v>
-      </c>
-      <c r="L19" s="7"/>
-      <c r="M19" s="7"/>
-      <c r="N19" s="7"/>
+      <c r="B19" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5">
+        <v>16</v>
+      </c>
+      <c r="J19" s="5">
+        <v>16</v>
+      </c>
+      <c r="K19" s="5">
+        <v>16</v>
+      </c>
+      <c r="L19" s="5"/>
+      <c r="M19" s="5"/>
+      <c r="N19" s="5"/>
       <c r="O19" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="P19" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Q19" s="5">
         <v>2200</v>
       </c>
-      <c r="R19" s="8" t="s">
-        <v>18</v>
+      <c r="R19" s="9" t="s">
+        <v>16</v>
       </c>
       <c r="S19" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="T19" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="U19" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="V19" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="W19" s="5">
         <v>10</v>
@@ -1683,50 +1652,50 @@
       <c r="A20" s="5">
         <v>15</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7">
-        <v>16</v>
-      </c>
-      <c r="J20" s="7">
-        <v>16</v>
-      </c>
-      <c r="K20" s="7">
-        <v>16</v>
-      </c>
-      <c r="L20" s="7"/>
-      <c r="M20" s="7"/>
-      <c r="N20" s="7"/>
+      <c r="B20" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5">
+        <v>16</v>
+      </c>
+      <c r="J20" s="5">
+        <v>16</v>
+      </c>
+      <c r="K20" s="5">
+        <v>16</v>
+      </c>
+      <c r="L20" s="5"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="5"/>
       <c r="O20" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="P20" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Q20" s="5">
         <v>2200</v>
       </c>
-      <c r="R20" s="8" t="s">
-        <v>18</v>
+      <c r="R20" s="9" t="s">
+        <v>16</v>
       </c>
       <c r="S20" s="5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T20" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="U20" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="V20" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="W20" s="5">
         <v>10</v>
@@ -1736,50 +1705,50 @@
       <c r="A21" s="5">
         <v>16</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7">
-        <v>16</v>
-      </c>
-      <c r="J21" s="7">
-        <v>16</v>
-      </c>
-      <c r="K21" s="7">
-        <v>16</v>
-      </c>
-      <c r="L21" s="7"/>
-      <c r="M21" s="7"/>
-      <c r="N21" s="7"/>
+      <c r="B21" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5">
+        <v>16</v>
+      </c>
+      <c r="J21" s="5">
+        <v>16</v>
+      </c>
+      <c r="K21" s="5">
+        <v>16</v>
+      </c>
+      <c r="L21" s="5"/>
+      <c r="M21" s="5"/>
+      <c r="N21" s="5"/>
       <c r="O21" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="P21" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Q21" s="5">
         <v>2200</v>
       </c>
-      <c r="R21" s="8" t="s">
-        <v>18</v>
+      <c r="R21" s="9" t="s">
+        <v>16</v>
       </c>
       <c r="S21" s="5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T21" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="U21" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="V21" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="W21" s="5">
         <v>10</v>
@@ -1789,50 +1758,50 @@
       <c r="A22" s="5">
         <v>17</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7">
-        <v>16</v>
-      </c>
-      <c r="J22" s="7">
-        <v>16</v>
-      </c>
-      <c r="K22" s="7">
-        <v>16</v>
-      </c>
-      <c r="L22" s="7"/>
-      <c r="M22" s="7"/>
-      <c r="N22" s="7"/>
+      <c r="B22" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5">
+        <v>16</v>
+      </c>
+      <c r="J22" s="5">
+        <v>16</v>
+      </c>
+      <c r="K22" s="5">
+        <v>16</v>
+      </c>
+      <c r="L22" s="5"/>
+      <c r="M22" s="5"/>
+      <c r="N22" s="5"/>
       <c r="O22" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="P22" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Q22" s="5">
         <v>2200</v>
       </c>
-      <c r="R22" s="8" t="s">
-        <v>18</v>
+      <c r="R22" s="9" t="s">
+        <v>16</v>
       </c>
       <c r="S22" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="T22" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="U22" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="V22" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="W22" s="5">
         <v>10</v>
@@ -1842,50 +1811,50 @@
       <c r="A23" s="5">
         <v>18</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-      <c r="I23" s="7">
-        <v>16</v>
-      </c>
-      <c r="J23" s="7">
-        <v>16</v>
-      </c>
-      <c r="K23" s="7">
-        <v>16</v>
-      </c>
-      <c r="L23" s="7"/>
-      <c r="M23" s="7"/>
-      <c r="N23" s="7"/>
+      <c r="B23" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5">
+        <v>16</v>
+      </c>
+      <c r="J23" s="5">
+        <v>16</v>
+      </c>
+      <c r="K23" s="5">
+        <v>16</v>
+      </c>
+      <c r="L23" s="5"/>
+      <c r="M23" s="5"/>
+      <c r="N23" s="5"/>
       <c r="O23" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="P23" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Q23" s="5">
         <v>2200</v>
       </c>
-      <c r="R23" s="8" t="s">
-        <v>18</v>
+      <c r="R23" s="9" t="s">
+        <v>16</v>
       </c>
       <c r="S23" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="T23" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="U23" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="V23" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="W23" s="5">
         <v>10</v>
@@ -1896,49 +1865,49 @@
         <v>19</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="7"/>
-      <c r="L24" s="7">
-        <v>16</v>
-      </c>
-      <c r="M24" s="7">
-        <v>16</v>
-      </c>
-      <c r="N24" s="7">
+        <v>42</v>
+      </c>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="5"/>
+      <c r="L24" s="5">
+        <v>16</v>
+      </c>
+      <c r="M24" s="5">
+        <v>16</v>
+      </c>
+      <c r="N24" s="5">
         <v>16</v>
       </c>
       <c r="O24" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="P24" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Q24" s="5">
         <v>3000</v>
       </c>
-      <c r="R24" s="8" t="s">
-        <v>18</v>
+      <c r="R24" s="9" t="s">
+        <v>16</v>
       </c>
       <c r="S24" s="5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T24" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="U24" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="V24" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="W24" s="5">
         <v>12</v>
@@ -1948,105 +1917,105 @@
       <c r="A25" s="5">
         <v>20</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
-      <c r="J25" s="7"/>
-      <c r="K25" s="7"/>
-      <c r="L25" s="7">
-        <v>16</v>
-      </c>
-      <c r="M25" s="7">
-        <v>16</v>
-      </c>
-      <c r="N25" s="7">
+      <c r="B25" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="5"/>
+      <c r="K25" s="5"/>
+      <c r="L25" s="5">
+        <v>16</v>
+      </c>
+      <c r="M25" s="5">
+        <v>16</v>
+      </c>
+      <c r="N25" s="5">
         <v>16</v>
       </c>
       <c r="O25" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="P25" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Q25" s="5">
         <v>3000</v>
       </c>
-      <c r="R25" s="8" t="s">
-        <v>18</v>
+      <c r="R25" s="9" t="s">
+        <v>16</v>
       </c>
       <c r="S25" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="T25" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="U25" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="V25" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="W25" s="5">
         <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:23" s="1" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A26" s="9">
+      <c r="A26" s="5">
         <v>21</v>
       </c>
-      <c r="B26" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="12"/>
-      <c r="H26" s="12"/>
-      <c r="I26" s="12"/>
-      <c r="J26" s="12"/>
-      <c r="K26" s="12"/>
-      <c r="L26" s="9">
-        <v>16</v>
-      </c>
-      <c r="M26" s="9">
-        <v>16</v>
-      </c>
-      <c r="N26" s="9">
-        <v>16</v>
-      </c>
-      <c r="O26" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="P26" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q26" s="12">
+      <c r="B26" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="10"/>
+      <c r="G26" s="10"/>
+      <c r="H26" s="10"/>
+      <c r="I26" s="10"/>
+      <c r="J26" s="10"/>
+      <c r="K26" s="10"/>
+      <c r="L26" s="5">
+        <v>16</v>
+      </c>
+      <c r="M26" s="5">
+        <v>16</v>
+      </c>
+      <c r="N26" s="5">
+        <v>16</v>
+      </c>
+      <c r="O26" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="P26" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q26" s="10">
         <v>3000</v>
       </c>
-      <c r="R26" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="S26" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="T26" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="U26" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="V26" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="W26" s="9">
+      <c r="R26" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="S26" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="T26" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="U26" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="V26" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="W26" s="5">
         <v>12</v>
       </c>
     </row>
@@ -2054,50 +2023,50 @@
       <c r="A27" s="5">
         <v>22</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="7"/>
-      <c r="I27" s="7"/>
-      <c r="J27" s="7"/>
-      <c r="K27" s="7"/>
-      <c r="L27" s="7">
-        <v>16</v>
-      </c>
-      <c r="M27" s="7">
-        <v>16</v>
-      </c>
-      <c r="N27" s="7">
+      <c r="B27" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="5"/>
+      <c r="K27" s="5"/>
+      <c r="L27" s="5">
+        <v>16</v>
+      </c>
+      <c r="M27" s="5">
+        <v>16</v>
+      </c>
+      <c r="N27" s="5">
         <v>16</v>
       </c>
       <c r="O27" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="P27" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Q27" s="5">
         <v>3000</v>
       </c>
-      <c r="R27" s="8" t="s">
-        <v>18</v>
+      <c r="R27" s="9" t="s">
+        <v>16</v>
       </c>
       <c r="S27" s="5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T27" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="U27" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="V27" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="W27" s="5">
         <v>12</v>
@@ -2107,50 +2076,50 @@
       <c r="A28" s="5">
         <v>23</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="7"/>
-      <c r="I28" s="7"/>
-      <c r="J28" s="7"/>
-      <c r="K28" s="7"/>
-      <c r="L28" s="7">
-        <v>16</v>
-      </c>
-      <c r="M28" s="7">
-        <v>16</v>
-      </c>
-      <c r="N28" s="7">
+      <c r="B28" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="5"/>
+      <c r="K28" s="5"/>
+      <c r="L28" s="5">
+        <v>16</v>
+      </c>
+      <c r="M28" s="5">
+        <v>16</v>
+      </c>
+      <c r="N28" s="5">
         <v>16</v>
       </c>
       <c r="O28" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="P28" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Q28" s="5">
         <v>3000</v>
       </c>
-      <c r="R28" s="8" t="s">
-        <v>18</v>
+      <c r="R28" s="9" t="s">
+        <v>16</v>
       </c>
       <c r="S28" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="T28" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="U28" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="V28" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="W28" s="5">
         <v>12</v>
